--- a/deploy/exemplos/Simplificado_12345678000199.xlsx
+++ b/deploy/exemplos/Simplificado_12345678000199.xlsx
@@ -26,6 +26,9 @@
   </x:si>
   <x:si>
     <x:t>12345678000199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Razão Social</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -376,12 +379,13 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C3"/>
+  <x:dimension ref="A1:D3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="15.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="12.460625" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="5.460625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -393,6 +397,9 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
